--- a/hasilsurvei.xlsx
+++ b/hasilsurvei.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\WO-VISIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6AF557B-C0BD-48EF-9AEB-F15EE4DDA196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363A5091-E340-4DF5-A299-F29BBB85A8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{6EF9AD42-8ECE-4260-B399-36B1C79DB1C7}"/>
   </bookViews>
@@ -39,7 +39,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>ID_NUMBER</t>
+  </si>
+  <si>
+    <t>CUSTOMER_NAME</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>REASON</t>
+  </si>
+  <si>
+    <t>SUB_REASON</t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>DATE_REPORT</t>
+  </si>
+  <si>
+    <t>FOTO</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -86,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
@@ -97,10 +122,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,14 +459,51 @@
   <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
